--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>입사기준: 개인별 입사기념일마다 근속연수가 갱신되어 그 시점에 연차가 부여됩니다. 회계기준: 전 직원이 회계연도 시작일에 일괄로 근속연수가 갱신되며, 입사연도에는 비례연차가 적용됩니다. 미입력 시 '입사기준'으로 계산됩니다.</t>
+          <t>입사기준: 개인별 입사기념일마다 근속연수가 갱신되어 그 시점에 연차가 전액 부여되고, 직전 기념일부터 결산기준일까지 진행 중인 다음 사이클도 경과월수만큼 안분 가산됩니다. 회계기준: 전 직원이 결산기준일(회계연도 종료일)에 일괄로 근속연수가 갱신되며, 입사연도에는 비례연차가 적용됩니다. 둘 다 발생주의(그 연차를 만든 근로가 제공된 회계기간 말에 인식) 기준입니다. 미입력 시 '입사기준'으로 계산됩니다.</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A91"/>
+  <dimension ref="A1:A97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,144 +2074,186 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       입사기준 — 개인별 입사기념일마다 근속연수가 갱신되어 그 시점에 연차가 개별 부여됩니다.</t>
+          <t xml:space="preserve">       입사기준 — 개인별 입사기념일마다 근속연수가 갱신되어 그 시점에 연차가 전액 개별 부여되고,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       회계기준 — 전 직원이 회계연도 시작일(전기 결산기준일 다음날)에 일괄로 근속연수가 갱신되어</t>
+          <t xml:space="preserve">         직전 확정 기념일부터 결산기준일까지 진행 중인 다음 사이클도 경과월수만큼(발생주의 월할)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         한 번에 부여받습니다. 입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례)가 적용됩니다.</t>
+          <t xml:space="preserve">         안분해 추가로 가산됩니다(예: 5/31 입사자, 결산일 12/31 → 다음 근속연수분 × 8/12 가산).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 지급률(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
+          <t xml:space="preserve">       회계기준 — 전 직원이 결산기준일(회계연도 종료일)에 일괄로 근속연수가 갱신되어 한 번에</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이행하면 미사용 연차의 금전 지급의무가 면제됩니다. 인원별 절차 이행 여부를 확인하기 어려우므로,</t>
+          <t xml:space="preserve">         부여받습니다(당기 근무로 발생하는 연차를 당기말에 인식 — 법적 사용가능일이 익년이라도).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     전사 공통으로 '실제 지급될 것으로 예상하는 비율(%)'을 입력하면 그 비율만큼만 충당부채로</t>
+          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례)가 적용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 연도마다 촉진 이행 여부·실제</t>
+          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     사용률이 달라질 수 있어 당기/전기 지급률을 각각 따로 입력받습니다 — 당기 지급률은 당기말</t>
+          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     충당부채(재계산)에, 전기 지급률은 전기말 충당부채(재계산)에 각각 적용됩니다. 촉진제도를 쓰지</t>
+          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
+          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 지급률(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
+          <t xml:space="preserve">     이행하면 미사용 연차의 금전 지급의무가 면제됩니다. 인원별 절차 이행 여부를 확인하기 어려우므로,</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
+          <t xml:space="preserve">     전사 공통으로 '실제 지급될 것으로 예상하는 비율(%)'을 입력하면 그 비율만큼만 충당부채로</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+          <t xml:space="preserve">     인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 연도마다 촉진 이행 여부·실제</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+          <t xml:space="preserve">     사용률이 달라질 수 있어 당기/전기 지급률을 각각 따로 입력받습니다 — 당기 지급률은 당기말</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
+          <t xml:space="preserve">     충당부채(재계산)에, 전기 지급률은 전기말 충당부채(재계산)에 각각 적용됩니다. 촉진제도를 쓰지</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="15" t="inlineStr"/>
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="15" t="inlineStr"/>
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
           <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="15" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) leave_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A97"/>
+  <dimension ref="A1:A99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2081,179 +2081,193 @@
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         직전 확정 기념일부터 결산기준일까지 진행 중인 다음 사이클도 경과월수만큼(발생주의 월할)</t>
+          <t xml:space="preserve">         직전 확정 기념일부터 결산기준일까지 '만 1개월 개근'이 완성된 횟수만큼(발생주의 월할,</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         안분해 추가로 가산됩니다(예: 5/31 입사자, 결산일 12/31 → 다음 근속연수분 × 8/12 가산).</t>
+          <t xml:space="preserve">         기념일 당일이 속한 첫 달은 하루만 근무했어도 카운트 안 함) 다음 사이클을 안분해 추가</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       회계기준 — 전 직원이 결산기준일(회계연도 종료일)에 일괄로 근속연수가 갱신되어 한 번에</t>
+          <t xml:space="preserve">         가산됩니다(예: 5/31 입사자, 결산일 12/31 → 6개월 뒤인 11/30까지 6개월 + 12/31 완성</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         부여받습니다(당기 근무로 발생하는 연차를 당기말에 인식 — 법적 사용가능일이 익년이라도).</t>
+          <t xml:space="preserve">         1개월 = 7개월 → 다음 근속연수분 × 7/12 가산).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례)가 적용됩니다.</t>
+          <t xml:space="preserve">       회계기준 — 전 직원이 결산기준일(회계연도 종료일)에 일괄로 근속연수가 갱신되어 한 번에</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
+          <t xml:space="preserve">         부여받습니다(당기 근무로 발생하는 연차를 당기말에 인식 — 법적 사용가능일이 익년이라도).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
+          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례)가 적용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
+          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 지급률(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
+          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이행하면 미사용 연차의 금전 지급의무가 면제됩니다. 인원별 절차 이행 여부를 확인하기 어려우므로,</t>
+          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     전사 공통으로 '실제 지급될 것으로 예상하는 비율(%)'을 입력하면 그 비율만큼만 충당부채로</t>
+          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 지급률(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 연도마다 촉진 이행 여부·실제</t>
+          <t xml:space="preserve">     이행하면 미사용 연차의 금전 지급의무가 면제됩니다. 인원별 절차 이행 여부를 확인하기 어려우므로,</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     사용률이 달라질 수 있어 당기/전기 지급률을 각각 따로 입력받습니다 — 당기 지급률은 당기말</t>
+          <t xml:space="preserve">     전사 공통으로 '실제 지급될 것으로 예상하는 비율(%)'을 입력하면 그 비율만큼만 충당부채로</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     충당부채(재계산)에, 전기 지급률은 전기말 충당부채(재계산)에 각각 적용됩니다. 촉진제도를 쓰지</t>
+          <t xml:space="preserve">     인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 연도마다 촉진 이행 여부·실제</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
+          <t xml:space="preserve">     사용률이 달라질 수 있어 당기/전기 지급률을 각각 따로 입력받습니다 — 당기 지급률은 당기말</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
+          <t xml:space="preserve">     충당부채(재계산)에, 전기 지급률은 전기말 충당부채(재계산)에 각각 적용됩니다. 촉진제도를 쓰지</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
+          <t xml:space="preserve">     않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
+          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="15" t="inlineStr"/>
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
-        </is>
-      </c>
+      <c r="A93" s="15" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="15" t="inlineStr"/>
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
           <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="15" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) leave_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A99"/>
+  <dimension ref="A1:A100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2123,151 +2123,158 @@
     <row r="77">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례)가 적용됩니다.</t>
+          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례, 개근 원칙 — 입사월이라도</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
+          <t xml:space="preserve">         하루만 근무했으면 그 달은 미포함)가 적용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
+          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
+          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 지급률(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
+          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이행하면 미사용 연차의 금전 지급의무가 면제됩니다. 인원별 절차 이행 여부를 확인하기 어려우므로,</t>
+          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 지급률(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     전사 공통으로 '실제 지급될 것으로 예상하는 비율(%)'을 입력하면 그 비율만큼만 충당부채로</t>
+          <t xml:space="preserve">     이행하면 미사용 연차의 금전 지급의무가 면제됩니다. 인원별 절차 이행 여부를 확인하기 어려우므로,</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 연도마다 촉진 이행 여부·실제</t>
+          <t xml:space="preserve">     전사 공통으로 '실제 지급될 것으로 예상하는 비율(%)'을 입력하면 그 비율만큼만 충당부채로</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     사용률이 달라질 수 있어 당기/전기 지급률을 각각 따로 입력받습니다 — 당기 지급률은 당기말</t>
+          <t xml:space="preserve">     인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 연도마다 촉진 이행 여부·실제</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     충당부채(재계산)에, 전기 지급률은 전기말 충당부채(재계산)에 각각 적용됩니다. 촉진제도를 쓰지</t>
+          <t xml:space="preserve">     사용률이 달라질 수 있어 당기/전기 지급률을 각각 따로 입력받습니다 — 당기 지급률은 당기말</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
+          <t xml:space="preserve">     충당부채(재계산)에, 전기 지급률은 전기말 충당부채(재계산)에 각각 적용됩니다. 촉진제도를 쓰지</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
+          <t xml:space="preserve">     않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
+          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="15" t="inlineStr"/>
-    </row>
     <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
-        </is>
-      </c>
+      <c r="A94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="15" t="inlineStr"/>
-    </row>
     <row r="98">
-      <c r="A98" s="15" t="inlineStr">
-        <is>
-          <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
-        </is>
-      </c>
+      <c r="A98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) leave_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -1498,26 +1498,26 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>당기 연차사용촉진 반영 지급률(%, 미입력시 100%)</t>
+          <t>당기 연차사용촉진 반영 부채인정비율(%, 미입력시 100%)</t>
         </is>
       </c>
       <c r="B6" s="11" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>연차사용촉진제도(근로기준법 제61조)를 적법하게 이행하면 미사용 연차에 대한 금전 지급의무가 면제됩니다. 인원별로 절차 이행 여부를 확인하기 어려우므로, 전사 공통으로 '당기 중 실제 지급될 것으로 예상하는 비율(%)'을 입력하면 이 비율만큼만 당기말 충당부채로 인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 예) 70 입력 시 당기말 잔여연차 금액의 70%만 충당부채로 인식. 촉진제도를 쓰지 않거나 비율을 모르면 비워두세요(100%로 계산됨).</t>
+          <t>연차사용촉진제도(근로기준법 제61조)를 적법하게 이행해도, 잔여연차 중 완전히 소멸(미사용+촉진 이행으로 금전보상의무까지 면제)되는 부분만 부채가 0입니다. 사용될 것으로 예상되는 부분은 그 유급휴가를 제공할 의무 자체가 이미 당기 근무의 대가로 발생했으므로(일반기준 21.5의2 매칭원칙 — 현금유출 여부와 무관), 미사용인데 촉진 실패로 금전보상해야 하는 부분과 함께 모두 부채로 남습니다. 인원별로 이 구성비를 확인하기 어려우므로, 전사 공통으로 '완전소멸되지 않고 부채로 남을 것으로 예상하는 비율(%) = 1 − 완전소멸 예상비율'을 입력하면 이 비율만큼만 당기말 충당부채로 인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 예) 70 입력 시 당기말 잔여연차 금액의 70%만 충당부채로 인식(30%는 미사용+촉진 적법이행으로 완전소멸 예상). 촉진제도를 쓰지 않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액 부채).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>전기 연차사용촉진 반영 지급률(%, 미입력시 100%)</t>
+          <t>전기 연차사용촉진 반영 부채인정비율(%, 미입력시 100%)</t>
         </is>
       </c>
       <c r="B7" s="11" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>위와 동일하되 전기말 충당부채 재계산에 적용되는 지급률입니다. 연도별로 촉진 이행 여부·실제 사용률이 달라질 수 있어 당기와 별도로 입력받습니다. 전기에는 촉진제도를 쓰지 않았거나 비율을 모르면 비워두세요(100%로 계산됨).</t>
+          <t>위와 동일하되 전기말 충당부채 재계산에 적용되는 부채인정비율입니다. 연도별로 촉진 이행 여부·실제 소멸률이 달라질 수 있어 당기와 별도로 입력받습니다. 전기에는 촉진제도를 쓰지 않았거나 비율을 모르면 비워두세요(100%로 계산됨).</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:A103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2158,123 +2158,144 @@
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 지급률(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
+          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 부채인정비율(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이행하면 미사용 연차의 금전 지급의무가 면제됩니다. 인원별 절차 이행 여부를 확인하기 어려우므로,</t>
+          <t xml:space="preserve">     이행해도, 잔여연차 중 완전히 소멸(미사용+촉진 이행으로 금전보상의무까지 면제)되는 부분만</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     전사 공통으로 '실제 지급될 것으로 예상하는 비율(%)'을 입력하면 그 비율만큼만 충당부채로</t>
+          <t xml:space="preserve">     부채가 0입니다. 사용될 것으로 예상되는 부분은 그 유급휴가를 제공할 의무 자체가 이미 당기</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐). 연도마다 촉진 이행 여부·실제</t>
+          <t xml:space="preserve">     근무의 대가로 발생했으므로(일반기준 21.5의2 매칭원칙, 현금유출 여부와 무관) 부채이고, 미사용</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     사용률이 달라질 수 있어 당기/전기 지급률을 각각 따로 입력받습니다 — 당기 지급률은 당기말</t>
+          <t xml:space="preserve">     인데 촉진 실패로 금전보상해야 하는 부분도 당연히 부채입니다. 인원별 구성비를 확인하기 어려우므로,</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     충당부채(재계산)에, 전기 지급률은 전기말 충당부채(재계산)에 각각 적용됩니다. 촉진제도를 쓰지</t>
+          <t xml:space="preserve">     전사 공통으로 '완전소멸되지 않고 부채로 남을 것으로 예상하는 비율(%) = 1−완전소멸 예상비율'을</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
+          <t xml:space="preserve">     입력하면 그 비율만큼만 충당부채로 인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
+          <t xml:space="preserve">     연도마다 촉진 이행 여부·실제 소멸률이 달라질 수 있어 당기/전기 비율을 각각 따로 입력받습니다 —</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
+          <t xml:space="preserve">     당기 비율은 당기말 충당부채(재계산)에, 전기 비율은 전기말 충당부채(재계산)에 각각 적용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+          <t xml:space="preserve">     촉진제도를 쓰지 않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
+          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="inlineStr"/>
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
-        </is>
-      </c>
+      <c r="A97" s="15" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="15" t="inlineStr"/>
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) leave_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -205,6 +205,52 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>leave_analyzer</author>
+  </authors>
+  <commentList>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>연차사용촉진 반영 부채인정비율 — 계산식 메모 (헷갈리기 쉬운 개념이라 예시로 설명)
+결산일 현재 잔여연차 1일은 다음 셋 중 하나로 귀결됩니다:
+  A. 실제 사용 예정 → 그 유급휴가를 줄 의무 자체가 이미 당기 근무의 대가로 발생
+     (일반기준 21.5의2 매칭원칙, 현금유출 여부와 무관) → 부채 O
+  B. 미사용인데 촉진 절차가 적법 이행돼 금전보상의무까지 완전 면제 → 부채 X (완전소멸)
+  C. 미사용인데 촉진 실패(절차 하자·퇴사자라 시간 없음·대상 제외 등) → 결국 현금 지급 → 부채 O
+부채인정비율 = (A+C) / (A+B+C) = 1 − B의 비율
+  ※ 자주 하는 실수: '미사용예상비율'(B+C)이나 '지급될 비율'(C)만 곱하는 것 — 틀립니다.
+    A(사용예정분)도 촉진과 무관하게 그 자체로 부채입니다.
+예시) 잔여연차 10일, 1일 통상임금 100,000원인 직원
+  A(사용예정) 7일 + C(미사용·지급예정) 2일 + B(완전소멸) 1일 = 10일
+  부채인정비율 = (7+2)/10 = 90%
+  연차충당부채 = 10일 × 100,000원 × 90% = 900,000원
+  (촉진 미적용이면 B=0이므로 100% 그대로 → 1,000,000원)</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>연차사용촉진 반영 부채인정비율 — 계산식 메모 (헷갈리기 쉬운 개념이라 예시로 설명)
+결산일 현재 잔여연차 1일은 다음 셋 중 하나로 귀결됩니다:
+  A. 실제 사용 예정 → 그 유급휴가를 줄 의무 자체가 이미 당기 근무의 대가로 발생
+     (일반기준 21.5의2 매칭원칙, 현금유출 여부와 무관) → 부채 O
+  B. 미사용인데 촉진 절차가 적법 이행돼 금전보상의무까지 완전 면제 → 부채 X (완전소멸)
+  C. 미사용인데 촉진 실패(절차 하자·퇴사자라 시간 없음·대상 제외 등) → 결국 현금 지급 → 부채 O
+부채인정비율 = (A+C) / (A+B+C) = 1 − B의 비율
+  ※ 자주 하는 실수: '미사용예상비율'(B+C)이나 '지급될 비율'(C)만 곱하는 것 — 틀립니다.
+    A(사용예정분)도 촉진과 무관하게 그 자체로 부채입니다.
+예시) 잔여연차 10일, 1일 통상임금 100,000원인 직원
+  A(사용예정) 7일 + C(미사용·지급예정) 2일 + B(완전소멸) 1일 = 10일
+  부채인정비율 = (7+2)/10 = 90%
+  연차충당부채 = 10일 × 100,000원 × 90% = 900,000원
+  (촉진 미적용이면 B=0이므로 100% 그대로 → 1,000,000원)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1617,6 +1663,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1626,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A103"/>
+  <dimension ref="A1:A108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2228,74 +2275,109 @@
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
+          <t xml:space="preserve">     [예시] 잔여연차 10일, 1일 통상임금 100,000원인 직원이 있다면: 7일은 내년 실사용 예정(부채 O),</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
+          <t xml:space="preserve">     2일은 미사용인데 촉진 실패로 결국 지급 예정(부채 O), 1일은 미사용+촉진 적법이행으로 완전소멸</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+          <t xml:space="preserve">     (부채 X) → 부채인정비율 = (7+2)/10 = 90% → 연차충당부채 = 10일×100,000원×90% = 900,000원.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+          <t xml:space="preserve">     ※ 흔한 실수: '미사용예상비율'(2+1일=30%)이나 '지급될 비율'(2일=20%)만 곱하면 사용예정분</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
+          <t xml:space="preserve">     7일치가 통째로 빠져 과소계상됩니다 — 이 셀(B열)에 마우스를 올리면 같은 예시가 메모로도 뜹니다.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="15" t="inlineStr"/>
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
         <is>
-          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="15" t="inlineStr"/>
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="inlineStr">
-        <is>
-          <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
-        </is>
-      </c>
+      <c r="A102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) leave_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -208,6 +208,50 @@
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>leave_analyzer</author>
+  </authors>
+  <commentList>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>'당기 연차사용일수' — 무엇을 적는 칸인지 헷갈리기 쉬워 메모로 설명
+이 칸은 이 시트가 나타내는 회계연도(당기정보=당기, 전기정보=전기) 한 해 동안 이 사람이
+'실제로 휴가로 소진한' 연차일수를 그대로 옮겨 적는 칸입니다 — 회사 연차관리대장·인사시스템에
+이미 기록돼 있는 과거 실적치이며, 반차는 0.5로 입력 가능합니다.
+※ 연차산정기준(회계기준/입사기준)이나 anchor_end·안분 같은 계산 로직과는 전혀 무관합니다.
+  그런 건 이 옆의 '당기부여일수'(입력란 아님, 앱이 자동 계산)에서 처리되고, 이 칸은 그 결과와
+  상관없이 그냥 '한 해 동안 몇 일 쉬었는지' 사실 그대로만 적으면 됩니다.
+  당기말 잔여연차일수(계산) = 기초 이월연차잔여일수(입력) + 당기부여일수(계산) − 이 칸(입력)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>leave_analyzer</author>
+  </authors>
+  <commentList>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>'당기 연차사용일수' — 무엇을 적는 칸인지 헷갈리기 쉬워 메모로 설명
+이 칸은 이 시트가 나타내는 회계연도(당기정보=당기, 전기정보=전기) 한 해 동안 이 사람이
+'실제로 휴가로 소진한' 연차일수를 그대로 옮겨 적는 칸입니다 — 회사 연차관리대장·인사시스템에
+이미 기록돼 있는 과거 실적치이며, 반차는 0.5로 입력 가능합니다.
+※ 연차산정기준(회계기준/입사기준)이나 anchor_end·안분 같은 계산 로직과는 전혀 무관합니다.
+  그런 건 이 옆의 '당기부여일수'(입력란 아님, 앱이 자동 계산)에서 처리되고, 이 칸은 그 결과와
+  상관없이 그냥 '한 해 동안 몇 일 쉬었는지' 사실 그대로만 적으면 됩니다.
+  당기말 잔여연차일수(계산) = 기초 이월연차잔여일수(입력) + 당기부여일수(계산) − 이 칸(입력)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>leave_analyzer</author>
@@ -879,6 +923,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1225,6 +1270,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -222,6 +222,13 @@
 ※ 연차산정기준(회계기준/입사기준)이나 anchor_end·안분 같은 계산 로직과는 전혀 무관합니다.
   그런 건 이 옆의 '당기부여일수'(입력란 아님, 앱이 자동 계산)에서 처리되고, 이 칸은 그 결과와
   상관없이 그냥 '한 해 동안 몇 일 쉬었는지' 사실 그대로만 적으면 됩니다.
+참고로 이론상 이 칸의 사용일수가 나올 수 있는 소스는 아래뿐입니다(당기부여일수는 결산일에야
+발생주의로 '인식'되는 것이라 당기 중엔 아직 실제로 쓸 수 있는 상태가 아니라서 제외됨):
+  1. 기초 이월연차잔여일수 — 당기 시작 전부터 이미 갖고 있던 잔액
+  2. (입사기준만) 당기 중 실제로 도래한 입사기념일 전액부여분 — 그 기념일부터 연말까지 사용 가능
+  3. (공통) 신규입사자 첫해 월단위발생분(또는 회계기준 비례연차) — 발생 즉시 바로 사용 가능
+다만 앱은 이 배치를 구분해서 계산하지 않고 기초이월+당기부여−당기사용으로 단순 차감만 하므로,
+이 칸엔 배치 구분 없이 회사 연차관리대장상 그 해 실제 총사용일수만 그대로 적으면 됩니다.
   당기말 잔여연차일수(계산) = 기초 이월연차잔여일수(입력) + 당기부여일수(계산) − 이 칸(입력)</t>
       </text>
     </comment>
@@ -244,6 +251,13 @@
 ※ 연차산정기준(회계기준/입사기준)이나 anchor_end·안분 같은 계산 로직과는 전혀 무관합니다.
   그런 건 이 옆의 '당기부여일수'(입력란 아님, 앱이 자동 계산)에서 처리되고, 이 칸은 그 결과와
   상관없이 그냥 '한 해 동안 몇 일 쉬었는지' 사실 그대로만 적으면 됩니다.
+참고로 이론상 이 칸의 사용일수가 나올 수 있는 소스는 아래뿐입니다(당기부여일수는 결산일에야
+발생주의로 '인식'되는 것이라 당기 중엔 아직 실제로 쓸 수 있는 상태가 아니라서 제외됨):
+  1. 기초 이월연차잔여일수 — 당기 시작 전부터 이미 갖고 있던 잔액
+  2. (입사기준만) 당기 중 실제로 도래한 입사기념일 전액부여분 — 그 기념일부터 연말까지 사용 가능
+  3. (공통) 신규입사자 첫해 월단위발생분(또는 회계기준 비례연차) — 발생 즉시 바로 사용 가능
+다만 앱은 이 배치를 구분해서 계산하지 않고 기초이월+당기부여−당기사용으로 단순 차감만 하므로,
+이 칸엔 배치 구분 없이 회사 연차관리대장상 그 해 실제 총사용일수만 그대로 적으면 됩니다.
   당기말 잔여연차일수(계산) = 기초 이월연차잔여일수(입력) + 당기부여일수(계산) − 이 칸(입력)</t>
       </text>
     </comment>

--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>실제지급액(원)</t>
+          <t>실제연차지급액(원)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A108"/>
+  <dimension ref="A1:A110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,388 +2056,402 @@
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제연차지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그 사람의 전기말 연차충당부채(계산)와 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급</t>
+          <t xml:space="preserve">   찾아 그 사람의 전기말 연차충당부채(계산)와 자동으로 비교(대사)해 요약표에 표시합니다. '실제연차</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   등은 '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면</t>
+          <t xml:space="preserve">   지급액'은 퇴직금 등 다른 정산 항목을 뺀 연차(미사용연차수당) 정산분만 입력해야 합니다 — 전기말</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   됩니다(해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+          <t xml:space="preserve">   연차충당부채(계산)와 1:1로 직접 비교되는 값이라, 퇴직금까지 섞어 넣으면 차이가 왜곡됩니다.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원에 한해 참고용으로 적어둘 수 있습니다.</t>
+          <t xml:space="preserve">   사업장/부서/직급 등은 '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다.</t>
+          <t xml:space="preserve">   됩니다(해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="15" t="inlineStr"/>
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원에 한해 참고용으로 적어둘 수 있습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>6. '급여대장인원명부' 시트 (선택) — 연차수당 대상인원(당기정보)과 기말 급여대장상 실제 인원이</t>
+          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   일치하는지 대사하려는 용도입니다. 회사로부터 기말 급여대장 인원명부를 엑셀로 받으면, 사업장/부서/</t>
-        </is>
-      </c>
+      <c r="A59" s="15" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   사번/성명/직급만 이 시트에 붙여넣으세요. 앱이 사번(없으면 성명) 기준으로 '당기정보'와 자동 대사해</t>
+          <t>6. '급여대장인원명부' 시트 (선택) — 연차수당 대상인원(당기정보)과 기말 급여대장상 실제 인원이</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   요약표에 '연차수당 대상인원 대사' 표를 추가합니다 — 급여대장에만 있으면(연차 대상 인원 누락 가능),</t>
+          <t xml:space="preserve">   일치하는지 대사하려는 용도입니다. 회사로부터 기말 급여대장 인원명부를 엑셀로 받으면, 사업장/부서/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기정보에만 있으면(당기 중 퇴사 등) 각각 원인 확인이 필요하다는 경고가 표시됩니다.</t>
+          <t xml:space="preserve">   사번/성명/직급만 이 시트에 붙여넣으세요. 앱이 사번(없으면 성명) 기준으로 '당기정보'와 자동 대사해</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   인원명부를 확보하지 못했다면 이 시트는 비워두고, 대신 '기준정보' 시트의 '기말 급여대장상</t>
+          <t xml:space="preserve">   요약표에 '연차수당 대상인원 대사' 표를 추가합니다 — 급여대장에만 있으면(연차 대상 인원 누락 가능),</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   총인원수(명부 미확보 시 참고용)'에 총원 숫자만 입력하세요 — 연차수당 대상인원수와 단순 총인원</t>
+          <t xml:space="preserve">   당기정보에만 있으면(당기 중 퇴사 등) 각각 원인 확인이 필요하다는 경고가 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   비교만 요약표에 표시됩니다(원인 파악은 수기로 확인). 둘 다 비워두면 이 대사 자체가 생략됩니다.</t>
+          <t xml:space="preserve">   인원명부를 확보하지 못했다면 이 시트는 비워두고, 대신 '기준정보' 시트의 '기말 급여대장상</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="inlineStr"/>
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   총인원수(명부 미확보 시 참고용)'에 총원 숫자만 입력하세요 — 연차수당 대상인원수와 단순 총인원</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>7. '기준정보' 시트</t>
+          <t xml:space="preserve">   비교만 요약표에 표시됩니다(원인 파악은 수기로 확인). 둘 다 비워두면 이 대사 자체가 생략됩니다.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   '연차산정기준'(전사 공통 설정, 드롭다운): '입사기준' 또는 '회계기준' 중 회사의 실제 운영 방식을</t>
-        </is>
-      </c>
+      <c r="A68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     선택하세요. 미입력 시 '입사기준'으로 계산됩니다.</t>
+          <t>7. '기준정보' 시트</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       입사기준 — 개인별 입사기념일마다 근속연수가 갱신되어 그 시점에 연차가 전액 개별 부여되고,</t>
+          <t xml:space="preserve">   '연차산정기준'(전사 공통 설정, 드롭다운): '입사기준' 또는 '회계기준' 중 회사의 실제 운영 방식을</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         직전 확정 기념일부터 결산기준일까지 '만 1개월 개근'이 완성된 횟수만큼(발생주의 월할,</t>
+          <t xml:space="preserve">     선택하세요. 미입력 시 '입사기준'으로 계산됩니다.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         기념일 당일이 속한 첫 달은 하루만 근무했어도 카운트 안 함) 다음 사이클을 안분해 추가</t>
+          <t xml:space="preserve">       입사기준 — 개인별 입사기념일마다 근속연수가 갱신되어 그 시점에 연차가 전액 개별 부여되고,</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         가산됩니다(예: 5/31 입사자, 결산일 12/31 → 6개월 뒤인 11/30까지 6개월 + 12/31 완성</t>
+          <t xml:space="preserve">         직전 확정 기념일부터 결산기준일까지 '만 1개월 개근'이 완성된 횟수만큼(발생주의 월할,</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         1개월 = 7개월 → 다음 근속연수분 × 7/12 가산).</t>
+          <t xml:space="preserve">         기념일 당일이 속한 첫 달은 하루만 근무했어도 카운트 안 함) 다음 사이클을 안분해 추가</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       회계기준 — 전 직원이 결산기준일(회계연도 종료일)에 일괄로 근속연수가 갱신되어 한 번에</t>
+          <t xml:space="preserve">         가산됩니다(예: 5/31 입사자, 결산일 12/31 → 6개월 뒤인 11/30까지 6개월 + 12/31 완성</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         부여받습니다(당기 근무로 발생하는 연차를 당기말에 인식 — 법적 사용가능일이 익년이라도).</t>
+          <t xml:space="preserve">         1개월 = 7개월 → 다음 근속연수분 × 7/12 가산).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례, 개근 원칙 — 입사월이라도</t>
+          <t xml:space="preserve">       회계기준 — 전 직원이 결산기준일(회계연도 종료일)에 일괄로 근속연수가 갱신되어 한 번에</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         하루만 근무했으면 그 달은 미포함)가 적용됩니다.</t>
+          <t xml:space="preserve">         부여받습니다(당기 근무로 발생하는 연차를 당기말에 인식 — 법적 사용가능일이 익년이라도).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
+          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례, 개근 원칙 — 입사월이라도</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
+          <t xml:space="preserve">         하루만 근무했으면 그 달은 미포함)가 적용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
+          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 부채인정비율(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
+          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이행해도, 잔여연차 중 완전히 소멸(미사용+촉진 이행으로 금전보상의무까지 면제)되는 부분만</t>
+          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     부채가 0입니다. 사용될 것으로 예상되는 부분은 그 유급휴가를 제공할 의무 자체가 이미 당기</t>
+          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 부채인정비율(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     근무의 대가로 발생했으므로(일반기준 21.5의2 매칭원칙, 현금유출 여부와 무관) 부채이고, 미사용</t>
+          <t xml:space="preserve">     이행해도, 잔여연차 중 완전히 소멸(미사용+촉진 이행으로 금전보상의무까지 면제)되는 부분만</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     인데 촉진 실패로 금전보상해야 하는 부분도 당연히 부채입니다. 인원별 구성비를 확인하기 어려우므로,</t>
+          <t xml:space="preserve">     부채가 0입니다. 사용될 것으로 예상되는 부분은 그 유급휴가를 제공할 의무 자체가 이미 당기</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     전사 공통으로 '완전소멸되지 않고 부채로 남을 것으로 예상하는 비율(%) = 1−완전소멸 예상비율'을</t>
+          <t xml:space="preserve">     근무의 대가로 발생했으므로(일반기준 21.5의2 매칭원칙, 현금유출 여부와 무관) 부채이고, 미사용</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     입력하면 그 비율만큼만 충당부채로 인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐).</t>
+          <t xml:space="preserve">     인데 촉진 실패로 금전보상해야 하는 부분도 당연히 부채입니다. 인원별 구성비를 확인하기 어려우므로,</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     연도마다 촉진 이행 여부·실제 소멸률이 달라질 수 있어 당기/전기 비율을 각각 따로 입력받습니다 —</t>
+          <t xml:space="preserve">     전사 공통으로 '완전소멸되지 않고 부채로 남을 것으로 예상하는 비율(%) = 1−완전소멸 예상비율'을</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     당기 비율은 당기말 충당부채(재계산)에, 전기 비율은 전기말 충당부채(재계산)에 각각 적용됩니다.</t>
+          <t xml:space="preserve">     입력하면 그 비율만큼만 충당부채로 인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     촉진제도를 쓰지 않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
+          <t xml:space="preserve">     연도마다 촉진 이행 여부·실제 소멸률이 달라질 수 있어 당기/전기 비율을 각각 따로 입력받습니다 —</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     [예시] 잔여연차 10일, 1일 통상임금 100,000원인 직원이 있다면: 7일은 내년 실사용 예정(부채 O),</t>
+          <t xml:space="preserve">     당기 비율은 당기말 충당부채(재계산)에, 전기 비율은 전기말 충당부채(재계산)에 각각 적용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     2일은 미사용인데 촉진 실패로 결국 지급 예정(부채 O), 1일은 미사용+촉진 적법이행으로 완전소멸</t>
+          <t xml:space="preserve">     촉진제도를 쓰지 않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (부채 X) → 부채인정비율 = (7+2)/10 = 90% → 연차충당부채 = 10일×100,000원×90% = 900,000원.</t>
+          <t xml:space="preserve">     [예시] 잔여연차 10일, 1일 통상임금 100,000원인 직원이 있다면: 7일은 내년 실사용 예정(부채 O),</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     ※ 흔한 실수: '미사용예상비율'(2+1일=30%)이나 '지급될 비율'(2일=20%)만 곱하면 사용예정분</t>
+          <t xml:space="preserve">     2일은 미사용인데 촉진 실패로 결국 지급 예정(부채 O), 1일은 미사용+촉진 적법이행으로 완전소멸</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     7일치가 통째로 빠져 과소계상됩니다 — 이 셀(B열)에 마우스를 올리면 같은 예시가 메모로도 뜹니다.</t>
+          <t xml:space="preserve">     (부채 X) → 부채인정비율 = (7+2)/10 = 90% → 연차충당부채 = 10일×100,000원×90% = 900,000원.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
+          <t xml:space="preserve">     ※ 흔한 실수: '미사용예상비율'(2+1일=30%)이나 '지급될 비율'(2일=20%)만 곱하면 사용예정분</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
+          <t xml:space="preserve">     7일치가 통째로 빠져 과소계상됩니다 — 이 셀(B열)에 마우스를 올리면 같은 예시가 메모로도 뜹니다.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
+          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="inlineStr"/>
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="inlineStr">
         <is>
-          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
-        </is>
-      </c>
+      <c r="A104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="15" t="inlineStr"/>
+      <c r="A106" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
           <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="15" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) leave_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
+++ b/account_analyzer/accrued_leave_liability_analyzer/input_data/leave_template.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -613,8 +613,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -645,7 +646,8 @@
           <t>대사용(선택)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -704,10 +706,15 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>회사계상 기말 연차일수(일)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>회사계상 기말 연차충당부채(원)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -758,12 +765,15 @@
       <c r="J3" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="K3" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L3" s="6" t="n">
         <v>600000</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — 실제 인원으로 교체(기존 재직자). 기초 이월연차잔여일수(전기말 이월분) 5일 + 당기 부여일수(계산) − 당기 사용 3일로 당기말 잔여가 자동 계산됨. '회사계상 기말 연차충당부채'를 채우면 앱 계산값과 자동 대사</t>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 실제 인원으로 교체(기존 재직자). 기초 이월연차잔여일수(전기말 이월분) 5일 + 당기 부여일수(계산) − 당기 사용 3일로 당기말 잔여가 자동 계산됨. '회사계상 기말 연차일수'·'회사계상 기말 연차충당부채'를 채우면 앱 계산값과 각각 자동 대사(일수 차이·금액 차이 둘 다 확인 가능)</t>
         </is>
       </c>
     </row>
@@ -812,10 +822,11 @@
       <c r="J4" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — 기존 재직자(회사계상액 모름 — 비워두면 대사만 생략)</t>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 기존 재직자(회사계상 일수·금액 모름 — 비워두면 대사만 생략)</t>
         </is>
       </c>
     </row>
@@ -864,8 +875,9 @@
       <c r="J5" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>예시) 당기 중 신규입사 — '전기정보'에는 없어 요약표의 '신규입사자 명단'에 자동 표시됨. 근속 1년 미만이므로 월단위 발생(또는 회계기준이면 비례연차)만 반영됨</t>
         </is>
@@ -916,8 +928,9 @@
       <c r="J6" s="6" t="n">
         <v>105000</v>
       </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>예시) 근속 3년 이상 — 근로기준법상 가산휴가가 자동 반영됨(3년차 16일, 5년차 17일 … 25일 한도)</t>
         </is>
@@ -926,9 +939,9 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="M1"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="K1"/>
-    <mergeCell ref="L1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
   <dataValidations count="1">
@@ -947,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -960,8 +973,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -992,7 +1006,8 @@
           <t>대사용(선택)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -1051,10 +1066,15 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>회사계상 기말 연차일수(일)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>회사계상 기말 연차충당부채(원)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1105,10 +1125,13 @@
       <c r="J3" s="6" t="n">
         <v>118000</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="K3" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" s="6" t="n">
         <v>580000</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>예시 행 — 당기와 동일 인원(전기 시점 데이터). 이 시트의 '기초 이월연차잔여일수'는 전전기말 이월분</t>
         </is>
@@ -1159,8 +1182,9 @@
       <c r="J4" s="6" t="n">
         <v>108000</v>
       </c>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>예시 행 — 당기와 동일 인원</t>
         </is>
@@ -1211,8 +1235,9 @@
       <c r="J5" s="6" t="n">
         <v>103000</v>
       </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>예시 행 — 당기와 동일 인원</t>
         </is>
@@ -1263,8 +1288,9 @@
       <c r="J6" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>예시) 당기 중 퇴사 — '당기정보'에는 이 사번이 없어 요약표의 '퇴사자 명단'에 자동 표시됨</t>
         </is>
@@ -1273,9 +1299,9 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="M1"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="K1"/>
-    <mergeCell ref="L1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
   <dataValidations count="1">
@@ -1733,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A110"/>
+  <dimension ref="A1:A113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1973,485 +1999,506 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '회사계상 기말 연차충당부채(원)' (선택): 회사가 인원별로 이미 계산해둔 연차충당부채를 알면</t>
+          <t xml:space="preserve">   '회사계상 기말 연차일수(일)' (선택): 회사 연차관리대장상 그 시점 잔여연차일수를 알면 채워</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     채워 넣으세요. '당기정보'에 채우면 당기말 계산값과, '전기정보'에 채우면 전기말 계산값과</t>
+          <t xml:space="preserve">     넣으세요. 앱이 계산한 '당기말/전기말 잔여연차일수(계산)'과 인별로 자동 대사되어 일수 차이가</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     인별로 자동 대사되어 '인원별추계명세'/'전기인원별추계명세' 시트에 차이가 표시되고</t>
+          <t xml:space="preserve">     표시됩니다 — 통상임금 오류와 무관하게 '일수 자체'가 맞는지만 따로 확인하고 싶을 때 유용합니다.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     유의차이는 노란색으로 강조됩니다. 모르면 비워둬도 앱 실행에는 문제 없습니다.</t>
+          <t xml:space="preserve">   '회사계상 기말 연차충당부채(원)' (선택): 회사가 인원별로 이미 계산해둔 연차충당부채(금액)를</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr"/>
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     알면 채워 넣으세요. '당기정보'에 채우면 당기말 계산값과, '전기정보'에 채우면 전기말 계산값과</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
+          <t xml:space="preserve">     인별로 자동 대사되어 '인원별추계명세'/'전기인원별추계명세' 시트에 일수차이·금액차이가 각각</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">     표시되고 유의차이는 노란색으로 강조됩니다. 둘 다 모르면 비워둬도 앱 실행에는 문제 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   퇴사자(자동 산출) = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
-        </is>
-      </c>
+      <c r="A45" s="15" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
+          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   요약표의 '퇴사자 명단 대사' 표는 이 자동 산출 명단과 '당기퇴사자' 시트(아래 5번, 사용자 입력) 명단을</t>
+          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   나란히 놓고 비교합니다 — 양쪽에 모두 있으면 비고에 '이상없음', 한쪽에만 있으면 원인을 표시합니다.</t>
+          <t xml:space="preserve">   퇴사자(자동 산출) = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr"/>
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>5. '당기퇴사자' 시트 (선택) — 퇴직 시 연차정산 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
+          <t xml:space="preserve">   요약표의 '퇴사자 명단 대사' 표는 이 자동 산출 명단과 '당기퇴사자' 시트(아래 5번, 사용자 입력) 명단을</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '사번'(없으면 성명) + '실제연차지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을</t>
+          <t xml:space="preserve">   나란히 놓고 비교합니다 — 양쪽에 모두 있으면 비고에 '이상없음', 한쪽에만 있으면 원인을 표시합니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   찾아 그 사람의 전기말 연차충당부채(계산)와 자동으로 비교(대사)해 요약표에 표시합니다. '실제연차</t>
-        </is>
-      </c>
+      <c r="A52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   지급액'은 퇴직금 등 다른 정산 항목을 뺀 연차(미사용연차수당) 정산분만 입력해야 합니다 — 전기말</t>
+          <t>5. '당기퇴사자' 시트 (선택) — 퇴직 시 연차정산 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   연차충당부채(계산)와 1:1로 직접 비교되는 값이라, 퇴직금까지 섞어 넣으면 차이가 왜곡됩니다.</t>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제연차지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   사업장/부서/직급 등은 '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면</t>
+          <t xml:space="preserve">   찾아 그 사람의 전기말 연차충당부채(계산)와 자동으로 비교(대사)해 요약표에 표시합니다. '실제연차</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   됩니다(해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+          <t xml:space="preserve">   지급액'은 퇴직금 등 다른 정산 항목을 뺀 연차(미사용연차수당) 정산분만 입력해야 합니다 — 전기말</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원에 한해 참고용으로 적어둘 수 있습니다.</t>
+          <t xml:space="preserve">   연차충당부채(계산)와 1:1로 직접 비교되는 값이라, 퇴직금까지 섞어 넣으면 차이가 왜곡됩니다.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다.</t>
+          <t xml:space="preserve">   사업장/부서/직급 등은 '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr"/>
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   됩니다(해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="15" t="inlineStr">
         <is>
-          <t>6. '급여대장인원명부' 시트 (선택) — 연차수당 대상인원(당기정보)과 기말 급여대장상 실제 인원이</t>
+          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원에 한해 참고용으로 적어둘 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   일치하는지 대사하려는 용도입니다. 회사로부터 기말 급여대장 인원명부를 엑셀로 받으면, 사업장/부서/</t>
+          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   사번/성명/직급만 이 시트에 붙여넣으세요. 앱이 사번(없으면 성명) 기준으로 '당기정보'와 자동 대사해</t>
-        </is>
-      </c>
+      <c r="A62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   요약표에 '연차수당 대상인원 대사' 표를 추가합니다 — 급여대장에만 있으면(연차 대상 인원 누락 가능),</t>
+          <t>6. '급여대장인원명부' 시트 (선택) — 연차수당 대상인원(당기정보)과 기말 급여대장상 실제 인원이</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기정보에만 있으면(당기 중 퇴사 등) 각각 원인 확인이 필요하다는 경고가 표시됩니다.</t>
+          <t xml:space="preserve">   일치하는지 대사하려는 용도입니다. 회사로부터 기말 급여대장 인원명부를 엑셀로 받으면, 사업장/부서/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   인원명부를 확보하지 못했다면 이 시트는 비워두고, 대신 '기준정보' 시트의 '기말 급여대장상</t>
+          <t xml:space="preserve">   사번/성명/직급만 이 시트에 붙여넣으세요. 앱이 사번(없으면 성명) 기준으로 '당기정보'와 자동 대사해</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   총인원수(명부 미확보 시 참고용)'에 총원 숫자만 입력하세요 — 연차수당 대상인원수와 단순 총인원</t>
+          <t xml:space="preserve">   요약표에 '연차수당 대상인원 대사' 표를 추가합니다 — 급여대장에만 있으면(연차 대상 인원 누락 가능),</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   비교만 요약표에 표시됩니다(원인 파악은 수기로 확인). 둘 다 비워두면 이 대사 자체가 생략됩니다.</t>
+          <t xml:space="preserve">   당기정보에만 있으면(당기 중 퇴사 등) 각각 원인 확인이 필요하다는 경고가 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="15" t="inlineStr"/>
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   인원명부를 확보하지 못했다면 이 시트는 비워두고, 대신 '기준정보' 시트의 '기말 급여대장상</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>7. '기준정보' 시트</t>
+          <t xml:space="preserve">   총인원수(명부 미확보 시 참고용)'에 총원 숫자만 입력하세요 — 연차수당 대상인원수와 단순 총인원</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '연차산정기준'(전사 공통 설정, 드롭다운): '입사기준' 또는 '회계기준' 중 회사의 실제 운영 방식을</t>
+          <t xml:space="preserve">   비교만 요약표에 표시됩니다(원인 파악은 수기로 확인). 둘 다 비워두면 이 대사 자체가 생략됩니다.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     선택하세요. 미입력 시 '입사기준'으로 계산됩니다.</t>
-        </is>
-      </c>
+      <c r="A71" s="15" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       입사기준 — 개인별 입사기념일마다 근속연수가 갱신되어 그 시점에 연차가 전액 개별 부여되고,</t>
+          <t>7. '기준정보' 시트</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         직전 확정 기념일부터 결산기준일까지 '만 1개월 개근'이 완성된 횟수만큼(발생주의 월할,</t>
+          <t xml:space="preserve">   '연차산정기준'(전사 공통 설정, 드롭다운): '입사기준' 또는 '회계기준' 중 회사의 실제 운영 방식을</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         기념일 당일이 속한 첫 달은 하루만 근무했어도 카운트 안 함) 다음 사이클을 안분해 추가</t>
+          <t xml:space="preserve">     선택하세요. 미입력 시 '입사기준'으로 계산됩니다.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         가산됩니다(예: 5/31 입사자, 결산일 12/31 → 6개월 뒤인 11/30까지 6개월 + 12/31 완성</t>
+          <t xml:space="preserve">       입사기준 — 개인별 입사기념일마다 근속연수가 갱신되어 그 시점에 연차가 전액 개별 부여되고,</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         1개월 = 7개월 → 다음 근속연수분 × 7/12 가산).</t>
+          <t xml:space="preserve">         직전 확정 기념일부터 결산기준일까지 '만 1개월 개근'이 완성된 횟수만큼(발생주의 월할,</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       회계기준 — 전 직원이 결산기준일(회계연도 종료일)에 일괄로 근속연수가 갱신되어 한 번에</t>
+          <t xml:space="preserve">         기념일 당일이 속한 첫 달은 하루만 근무했어도 카운트 안 함) 다음 사이클을 안분해 추가</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         부여받습니다(당기 근무로 발생하는 연차를 당기말에 인식 — 법적 사용가능일이 익년이라도).</t>
+          <t xml:space="preserve">         가산됩니다(예: 5/31 입사자, 결산일 12/31 → 6개월 뒤인 11/30까지 6개월 + 12/31 완성</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례, 개근 원칙 — 입사월이라도</t>
+          <t xml:space="preserve">         1개월 = 7개월 → 다음 근속연수분 × 7/12 가산).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         하루만 근무했으면 그 달은 미포함)가 적용됩니다.</t>
+          <t xml:space="preserve">       회계기준 — 전 직원이 결산기준일(회계연도 종료일)에 일괄로 근속연수가 갱신되어 한 번에</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
+          <t xml:space="preserve">         부여받습니다(당기 근무로 발생하는 연차를 당기말에 인식 — 법적 사용가능일이 익년이라도).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
+          <t xml:space="preserve">         입사연도(근속연수 0년차)에는 비례연차(재직개월수 비례, 개근 원칙 — 입사월이라도</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
+          <t xml:space="preserve">         하루만 근무했으면 그 달은 미포함)가 적용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 부채인정비율(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
+          <t xml:space="preserve">       ※ 두 기준 모두 발생주의(K-IFRS 1019/일반기준 21장 누적유급휴가 원칙) — 그 연차를 만든</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이행해도, 잔여연차 중 완전히 소멸(미사용+촉진 이행으로 금전보상의무까지 면제)되는 부분만</t>
+          <t xml:space="preserve">         근로가 제공된 회계기간 말에 부채로 인식하며, 근로기준법상 법적 청구권 발생일(대개 익년</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     부채가 0입니다. 사용될 것으로 예상되는 부분은 그 유급휴가를 제공할 의무 자체가 이미 당기</t>
+          <t xml:space="preserve">         1/1 또는 입사기념일 다음날)과는 무관합니다.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     근무의 대가로 발생했으므로(일반기준 21.5의2 매칭원칙, 현금유출 여부와 무관) 부채이고, 미사용</t>
+          <t xml:space="preserve">   '당기/전기 연차사용촉진 반영 부채인정비율(%)': 연차사용촉진제도(근로기준법 제61조)를 적법하게</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     인데 촉진 실패로 금전보상해야 하는 부분도 당연히 부채입니다. 인원별 구성비를 확인하기 어려우므로,</t>
+          <t xml:space="preserve">     이행해도, 잔여연차 중 완전히 소멸(미사용+촉진 이행으로 금전보상의무까지 면제)되는 부분만</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     전사 공통으로 '완전소멸되지 않고 부채로 남을 것으로 예상하는 비율(%) = 1−완전소멸 예상비율'을</t>
+          <t xml:space="preserve">     부채가 0입니다. 사용될 것으로 예상되는 부분은 그 유급휴가를 제공할 의무 자체가 이미 당기</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     입력하면 그 비율만큼만 충당부채로 인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐).</t>
+          <t xml:space="preserve">     근무의 대가로 발생했으므로(일반기준 21.5의2 매칭원칙, 현금유출 여부와 무관) 부채이고, 미사용</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     연도마다 촉진 이행 여부·실제 소멸률이 달라질 수 있어 당기/전기 비율을 각각 따로 입력받습니다 —</t>
+          <t xml:space="preserve">     인데 촉진 실패로 금전보상해야 하는 부분도 당연히 부채입니다. 인원별 구성비를 확인하기 어려우므로,</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     당기 비율은 당기말 충당부채(재계산)에, 전기 비율은 전기말 충당부채(재계산)에 각각 적용됩니다.</t>
+          <t xml:space="preserve">     전사 공통으로 '완전소멸되지 않고 부채로 남을 것으로 예상하는 비율(%) = 1−완전소멸 예상비율'을</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     촉진제도를 쓰지 않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
+          <t xml:space="preserve">     입력하면 그 비율만큼만 충당부채로 인식합니다(잔여일수 자체는 그대로 표시되고 금액에만 곱해짐).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     [예시] 잔여연차 10일, 1일 통상임금 100,000원인 직원이 있다면: 7일은 내년 실사용 예정(부채 O),</t>
+          <t xml:space="preserve">     연도마다 촉진 이행 여부·실제 소멸률이 달라질 수 있어 당기/전기 비율을 각각 따로 입력받습니다 —</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     2일은 미사용인데 촉진 실패로 결국 지급 예정(부채 O), 1일은 미사용+촉진 적법이행으로 완전소멸</t>
+          <t xml:space="preserve">     당기 비율은 당기말 충당부채(재계산)에, 전기 비율은 전기말 충당부채(재계산)에 각각 적용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (부채 X) → 부채인정비율 = (7+2)/10 = 90% → 연차충당부채 = 10일×100,000원×90% = 900,000원.</t>
+          <t xml:space="preserve">     촉진제도를 쓰지 않거나 비율을 모르면 비워두세요(100%로 계산 — 잔여연차 전액을 충당부채로 인식).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     ※ 흔한 실수: '미사용예상비율'(2+1일=30%)이나 '지급될 비율'(2일=20%)만 곱하면 사용예정분</t>
+          <t xml:space="preserve">     [예시] 잔여연차 10일, 1일 통상임금 100,000원인 직원이 있다면: 7일은 내년 실사용 예정(부채 O),</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     7일치가 통째로 빠져 과소계상됩니다 — 이 셀(B열)에 마우스를 올리면 같은 예시가 메모로도 뜹니다.</t>
+          <t xml:space="preserve">     2일은 미사용인데 촉진 실패로 결국 지급 예정(부채 O), 1일은 미사용+촉진 적법이행으로 완전소멸</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
+          <t xml:space="preserve">     (부채 X) → 부채인정비율 = (7+2)/10 = 90% → 연차충당부채 = 10일×100,000원×90% = 900,000원.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
+          <t xml:space="preserve">     ※ 흔한 실수: '미사용예상비율'(2+1일=30%)이나 '지급될 비율'(2일=20%)만 곱하면 사용예정분</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+          <t xml:space="preserve">     7일치가 통째로 빠져 과소계상됩니다 — 이 셀(B열)에 마우스를 올리면 같은 예시가 메모로도 뜹니다.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
+          <t xml:space="preserve">   전기말/당기말 회사계상 연차충당부채(제조원가분/판관비분) 4칸과, 당기 연차충당부채 차변(당기지급액)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
+          <t xml:space="preserve">   1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체에는</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="15" t="inlineStr"/>
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   반영되지 않습니다. '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 관련 계정의 당기 차변</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="15" t="inlineStr">
         <is>
-          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   합계를 뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 연차수당비용(재계산)-당기지급액이 당기말</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   (회사계상)과 맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
-        </is>
-      </c>
+      <c r="A107" s="15" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="15" t="inlineStr"/>
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>8. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="15" t="inlineStr">
         <is>
-          <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+          <t xml:space="preserve">   severance_analyzer/depreciation_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>9. 파일명 규칙: 이 템플릿을 복사해 'leave_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) leave_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>
